--- a/artfynd/A 37926-2025 artfynd.xlsx
+++ b/artfynd/A 37926-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165967</v>
       </c>
       <c r="B2" t="n">
-        <v>91537</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129166399</v>
       </c>
       <c r="B3" t="n">
-        <v>80012</v>
+        <v>80013</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129165593</v>
       </c>
       <c r="B4" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129166337</v>
       </c>
       <c r="B5" t="n">
-        <v>88923</v>
+        <v>88926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129166093</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37926-2025 artfynd.xlsx
+++ b/artfynd/A 37926-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165967</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129166399</v>
       </c>
       <c r="B3" t="n">
-        <v>80013</v>
+        <v>80017</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129165593</v>
       </c>
       <c r="B4" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129166337</v>
       </c>
       <c r="B5" t="n">
-        <v>88926</v>
+        <v>88930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129166093</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37926-2025 artfynd.xlsx
+++ b/artfynd/A 37926-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165967</v>
       </c>
       <c r="B2" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129165593</v>
       </c>
       <c r="B4" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129166337</v>
       </c>
       <c r="B5" t="n">
-        <v>88930</v>
+        <v>88937</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37926-2025 artfynd.xlsx
+++ b/artfynd/A 37926-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165967</v>
       </c>
       <c r="B2" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129166399</v>
       </c>
       <c r="B3" t="n">
-        <v>80017</v>
+        <v>80019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129165593</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129166337</v>
       </c>
       <c r="B5" t="n">
-        <v>88937</v>
+        <v>88939</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129166093</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
